--- a/Result/profitability/6667.xlsx
+++ b/Result/profitability/6667.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM40"/>
+  <dimension ref="A1:AM41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5510,6 +5510,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>6667</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1676</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1298</v>
+      </c>
+      <c r="E41" t="n">
+        <v>379</v>
+      </c>
+      <c r="F41" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="G41" t="n">
+        <v>139</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>8.28%</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>104</v>
+      </c>
+      <c r="J41" t="n">
+        <v>243</v>
+      </c>
+      <c r="K41" t="n">
+        <v>200</v>
+      </c>
+      <c r="L41" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.41125</v>
+      </c>
+      <c r="N41" t="n">
+        <v>21.80625</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.4299999999999997</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.1184573002754821</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>-1.390000000000001</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-0.05796497080900753</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.6399999999999997</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.1871345029239766</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.550000000000001</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.07366920152091261</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK41" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
